--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.370234565214</v>
+        <v>7.372663116847275</v>
       </c>
       <c r="D2" t="n">
-        <v>41.02855092380801</v>
+        <v>6.667139525118801</v>
       </c>
       <c r="E2" t="n">
-        <v>1.354372468956825</v>
+        <v>0.2200855262054842</v>
       </c>
       <c r="F2" t="n">
-        <v>5.356799119566322</v>
+        <v>0.8704798569295273</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.07897950312765</v>
+        <v>7.812834169258243</v>
       </c>
       <c r="D3" t="n">
-        <v>51.74214916294065</v>
+        <v>8.408099238977856</v>
       </c>
       <c r="E3" t="n">
-        <v>1.354372468956825</v>
+        <v>0.2200855262054842</v>
       </c>
       <c r="F3" t="n">
-        <v>5.356799119566322</v>
+        <v>0.8704798569295273</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
